--- a/data_generation/10_aquatic_toxicity/boscalid_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/boscalid_aquatic_toxicity.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U80868656\Documents\aquatic_tox_July_2026_mamr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFC1C11-EDAE-4DD5-8047-610C6BE8AA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB49A4AF-E024-4980-8CB6-7600752C1667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DCCE98E3-7ECB-464D-B3A9-333AAEFCC845}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabelle1!$A$1:$X$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="84">
   <si>
     <t>substance</t>
   </si>
@@ -265,6 +271,27 @@
   </si>
   <si>
     <t>Converted from preparation endpoint</t>
+  </si>
+  <si>
+    <t>Oncorhynchus mykiss</t>
+  </si>
+  <si>
+    <t>Lepomis macrochirus</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>Cyprinodon variegatus</t>
+  </si>
+  <si>
+    <t>97 d</t>
+  </si>
+  <si>
+    <t>early life stage</t>
+  </si>
+  <si>
+    <t>mortality, behaviour</t>
   </si>
 </sst>
 </file>
@@ -356,9 +383,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -396,7 +423,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -502,7 +529,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -644,7 +671,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -652,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA08FB3-CDA8-4307-B6A0-0CD6CA31604F}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -752,587 +779,542 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="2">
-        <v>5.33</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="M2">
+        <v>2.7</v>
+      </c>
+      <c r="N2" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" t="s">
         <v>46</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>115</v>
+      <c r="P2" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q2">
+        <v>114</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="3">
-        <v>115</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="S2">
+        <v>114</v>
+      </c>
+      <c r="T2" t="s">
         <v>44</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="3"/>
       <c r="W2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="2">
-        <v>3.81</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>115</v>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3">
+        <v>114</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S3" s="3">
-        <v>115</v>
-      </c>
-      <c r="T3" s="3" t="s">
+      <c r="S3">
+        <v>114</v>
+      </c>
+      <c r="T3" t="s">
         <v>44</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V3" s="3"/>
       <c r="W3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
+      <c r="I4" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="N4" s="3" t="s">
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="N4" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>115</v>
+      <c r="P4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q4">
+        <v>114</v>
       </c>
       <c r="R4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="3">
-        <v>115</v>
-      </c>
-      <c r="T4" s="3" t="s">
+      <c r="S4">
+        <v>114</v>
+      </c>
+      <c r="T4" t="s">
         <v>44</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V4" s="3"/>
       <c r="W4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="2">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="2">
-        <v>25.65</v>
-      </c>
-      <c r="N5" s="3" t="s">
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M5">
+        <v>5.9</v>
+      </c>
+      <c r="N5" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>115</v>
+      <c r="O5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5">
+        <v>114</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S5" s="3">
-        <v>115</v>
-      </c>
-      <c r="T5" s="3" t="s">
+      <c r="S5">
+        <v>114</v>
+      </c>
+      <c r="T5" t="s">
         <v>44</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="W5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="X5" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="M6" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="N6" s="3" t="s">
+      <c r="M6">
+        <v>4.34</v>
+      </c>
+      <c r="N6" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>115</v>
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q6">
+        <v>114</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S6" s="3">
-        <v>115</v>
-      </c>
-      <c r="T6" s="3" t="s">
+      <c r="S6">
+        <v>114</v>
+      </c>
+      <c r="T6" t="s">
         <v>44</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V6" s="3"/>
       <c r="W6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="2">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M7" s="2">
-        <v>1.31</v>
-      </c>
-      <c r="N7" s="3" t="s">
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7">
+        <v>3.86</v>
+      </c>
+      <c r="N7" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>115</v>
+      <c r="P7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7">
+        <v>114</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S7" s="3">
-        <v>115</v>
-      </c>
-      <c r="T7" s="3" t="s">
+      <c r="S7">
+        <v>114</v>
+      </c>
+      <c r="T7" t="s">
         <v>44</v>
       </c>
       <c r="U7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V7" s="3"/>
       <c r="W7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="X7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="2">
-        <v>7</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="2">
-        <v>97</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>115</v>
+      <c r="L8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
+        <v>51.3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" t="s">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8">
+        <v>114</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S8" s="3">
-        <v>115</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="V8" s="3"/>
+      <c r="S8">
+        <v>114</v>
+      </c>
+      <c r="T8" t="s">
+        <v>44</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="W8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="J9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="M9">
+        <v>0.125</v>
+      </c>
+      <c r="N9" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="O9" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>115</v>
+      <c r="P9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q9">
+        <v>114</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S9" s="3">
-        <v>115</v>
-      </c>
-      <c r="T9" s="3" t="s">
+      <c r="S9">
+        <v>114</v>
+      </c>
+      <c r="T9" t="s">
         <v>44</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V9" s="3"/>
       <c r="W9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="X9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>68</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>49</v>
       </c>
       <c r="M10" s="2">
-        <v>23.26</v>
+        <v>5.33</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Q10" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S10" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>65</v>
+        <v>44</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="s">
@@ -1342,37 +1324,37 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M11" s="2">
-        <v>2.61</v>
+        <v>3.81</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>26</v>
@@ -1384,13 +1366,13 @@
         <v>53</v>
       </c>
       <c r="Q11" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R11" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S11" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>44</v>
@@ -1406,27 +1388,27 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2">
         <v>10</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
@@ -1436,7 +1418,7 @@
         <v>49</v>
       </c>
       <c r="M12" s="2">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>26</v>
@@ -1448,13 +1430,13 @@
         <v>53</v>
       </c>
       <c r="Q12" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S12" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>44</v>
@@ -1470,13 +1452,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2">
         <v>11</v>
@@ -1486,37 +1470,39 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="2">
-        <v>3.5</v>
+        <v>25.65</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P13" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Q13" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R13" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S13" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>44</v>
@@ -1525,7 +1511,7 @@
         <v>66</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="W13" s="3" t="s">
         <v>52</v>
@@ -1534,39 +1520,37 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
         <v>12</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>49</v>
       </c>
       <c r="M14" s="2">
-        <v>2.31</v>
+        <v>0.8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>26</v>
@@ -1578,13 +1562,13 @@
         <v>53</v>
       </c>
       <c r="Q14" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S14" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>44</v>
@@ -1592,9 +1576,7 @@
       <c r="U14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="V14" s="3"/>
       <c r="W14" s="3" t="s">
         <v>52</v>
       </c>
@@ -1602,58 +1584,55 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="2">
-        <f>3.37*(2.31/4.5)</f>
-        <v>1.7299333333333333</v>
+        <v>1.31</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P15" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Q15" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S15" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>44</v>
@@ -1661,9 +1640,7 @@
       <c r="U15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>76</v>
-      </c>
+      <c r="V15" s="3"/>
       <c r="W15" s="3" t="s">
         <v>52</v>
       </c>
@@ -1671,42 +1648,42 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="G16" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>47</v>
       </c>
       <c r="M16" s="2">
-        <v>3.9</v>
+        <v>97</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>46</v>
@@ -1715,19 +1692,19 @@
         <v>53</v>
       </c>
       <c r="Q16" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S16" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="s">
@@ -1737,30 +1714,32 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="90" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D17" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="G17" s="3" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>28</v>
@@ -1769,25 +1748,25 @@
         <v>49</v>
       </c>
       <c r="M17" s="2">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P17" s="4" t="s">
         <v>53</v>
       </c>
       <c r="Q17" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R17" s="4" t="s">
         <v>53</v>
       </c>
       <c r="S17" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>44</v>
@@ -1803,55 +1782,585 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+    <row r="18" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M18" s="2">
+        <v>23.26</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>116</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S18" s="3">
+        <v>116</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
+      <c r="W18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="2">
+        <v>17</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M19" s="2">
+        <v>2.61</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>116</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S19" s="3">
+        <v>116</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
+      <c r="W19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="2">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1.33</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>116</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S20" s="3">
+        <v>116</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2">
+        <v>19</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M21" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>116</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S21" s="3">
+        <v>116</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="2">
+        <v>20</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="2">
+        <v>2.31</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>116</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S22" s="3">
+        <v>116</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="2">
+        <v>21</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M23" s="2">
+        <f>3.37*(2.31/4.5)</f>
+        <v>1.7299333333333333</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>116</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S23" s="3">
+        <v>116</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="2">
+        <v>22</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>116</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S24" s="3">
+        <v>116</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2">
+        <v>23</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>116</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S25" s="3">
+        <v>116</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:X1" xr:uid="{0CA08FB3-CDA8-4307-B6A0-0CD6CA31604F}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>